--- a/Retraite_25Meilleures_Annees_2023.xlsx
+++ b/Retraite_25Meilleures_Annees_2023.xlsx
@@ -29,10 +29,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,13 +63,13 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,13 +435,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,15 +453,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Salaire brut (FRF)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Salaire brut (EUR)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Coefficient 2023</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Montant au 1/1/2023</t>
         </is>
@@ -471,12 +477,15 @@
         <v>1990</v>
       </c>
       <c r="B2" s="2" t="n">
+        <v>68232.00319999999</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>10401.22</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>16329.91</v>
       </c>
     </row>
@@ -485,12 +494,15 @@
         <v>1991</v>
       </c>
       <c r="B3" s="2" t="n">
+        <v>112024.0048</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>17076.83</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>1.547</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>26417.85</v>
       </c>
     </row>
@@ -499,12 +511,15 @@
         <v>1992</v>
       </c>
       <c r="B4" s="2" t="n">
+        <v>103828.9904</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>15827.59</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>1.496</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>23678.08</v>
       </c>
     </row>
@@ -513,12 +528,15 @@
         <v>1993</v>
       </c>
       <c r="B5" s="2" t="n">
+        <v>99461.9984</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>15161.89</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>1.496</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>22682.19</v>
       </c>
     </row>
@@ -527,12 +545,15 @@
         <v>1994</v>
       </c>
       <c r="B6" s="2" t="n">
+        <v>139800.0288</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>21310.98</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>1.47</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>31327.13</v>
       </c>
     </row>
@@ -541,12 +562,15 @@
         <v>1995</v>
       </c>
       <c r="B7" s="2" t="n">
+        <v>518657.0192</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>79063.57000000001</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.453</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>114879.36</v>
       </c>
     </row>
@@ -555,12 +579,15 @@
         <v>1996</v>
       </c>
       <c r="B8" s="2" t="n">
+        <v>146554.008</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>22340.55</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>1.418</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>31678.9</v>
       </c>
     </row>
@@ -569,12 +596,15 @@
         <v>1997</v>
       </c>
       <c r="B9" s="2" t="n">
+        <v>92033.97919999999</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>14029.57</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>1.403</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>19683.49</v>
       </c>
     </row>
@@ -583,12 +613,15 @@
         <v>1999</v>
       </c>
       <c r="B10" s="2" t="n">
+        <v>103974.032</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>15849.7</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>1.371</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>21729.93</v>
       </c>
     </row>
@@ -596,13 +629,13 @@
       <c r="A11" t="n">
         <v>2002</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>33538</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>1.307</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>43834.17</v>
       </c>
     </row>
@@ -610,13 +643,13 @@
       <c r="A12" t="n">
         <v>2003</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="C12" s="2" t="n">
         <v>16007</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>1.286</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>20585</v>
       </c>
     </row>
@@ -624,13 +657,13 @@
       <c r="A13" t="n">
         <v>2004</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="C13" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>1.266</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>22788</v>
       </c>
     </row>
@@ -638,13 +671,13 @@
       <c r="A14" t="n">
         <v>2005</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>1.243</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="E14" s="2" t="n">
         <v>22374</v>
       </c>
     </row>
@@ -652,13 +685,13 @@
       <c r="A15" t="n">
         <v>2006</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>22000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>1.221</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>26862</v>
       </c>
     </row>
@@ -666,13 +699,13 @@
       <c r="A16" t="n">
         <v>2007</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="C16" s="2" t="n">
         <v>17289</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1.201</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>20764.09</v>
       </c>
     </row>
@@ -680,13 +713,13 @@
       <c r="A17" t="n">
         <v>2008</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="C17" s="2" t="n">
         <v>15084</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>1.189</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>17934.88</v>
       </c>
     </row>
@@ -694,13 +727,13 @@
       <c r="A18" t="n">
         <v>2010</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="C18" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>1.168</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="E18" s="2" t="n">
         <v>21024</v>
       </c>
     </row>
@@ -708,13 +741,13 @@
       <c r="A19" t="n">
         <v>2011</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="C19" s="2" t="n">
         <v>21000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>1.158</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="E19" s="2" t="n">
         <v>24318</v>
       </c>
     </row>
@@ -722,13 +755,13 @@
       <c r="A20" t="n">
         <v>2012</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="C20" s="2" t="n">
         <v>27200</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>1.135</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="E20" s="2" t="n">
         <v>30872</v>
       </c>
     </row>
@@ -736,13 +769,13 @@
       <c r="A21" t="n">
         <v>2013</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="C21" s="2" t="n">
         <v>33600</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>1.112</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="E21" s="2" t="n">
         <v>37363.2</v>
       </c>
     </row>
@@ -750,13 +783,13 @@
       <c r="A22" t="n">
         <v>2014</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="C22" s="2" t="n">
         <v>36000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>1.098</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="E22" s="2" t="n">
         <v>39528</v>
       </c>
     </row>
@@ -764,13 +797,13 @@
       <c r="A23" t="n">
         <v>2015</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="C23" s="2" t="n">
         <v>36000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>1.098</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="E23" s="2" t="n">
         <v>39528</v>
       </c>
     </row>
@@ -778,13 +811,13 @@
       <c r="A24" t="n">
         <v>2016</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="C24" s="2" t="n">
         <v>36000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>1.097</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="E24" s="2" t="n">
         <v>39492</v>
       </c>
     </row>
@@ -792,13 +825,13 @@
       <c r="A25" t="n">
         <v>2017</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="C25" s="2" t="n">
         <v>36000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>1.097</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="E25" s="2" t="n">
         <v>39492</v>
       </c>
     </row>
@@ -806,13 +839,13 @@
       <c r="A26" t="n">
         <v>2018</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="C26" s="2" t="n">
         <v>39000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>1.089</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="E26" s="2" t="n">
         <v>42471</v>
       </c>
     </row>
@@ -822,12 +855,27 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B27" s="5">
-        <f>SUM(B2:B26)</f>
+      <c r="C27" s="5">
+        <f>SUM(C2:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="5">
-        <f>SUM(D2:D26)</f>
+      <c r="E27" s="5">
+        <f>SUM(E2:E26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="C28" s="5">
+        <f>AVERAGE(C2:C26)</f>
+        <v/>
+      </c>
+      <c r="E28" s="5">
+        <f>AVERAGE(E2:E26)</f>
         <v/>
       </c>
     </row>

--- a/Retraite_25Meilleures_Annees_2023.xlsx
+++ b/Retraite_25Meilleures_Annees_2023.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="270" yWindow="550" windowWidth="18640" windowHeight="6740" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25 meilleures années" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +15,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ _€"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,11 +29,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -44,12 +59,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,22 +72,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -435,23 +476,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6.1796875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="15.54296875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="19.1796875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="19" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Année</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Salaire brut (FRF)</t>
         </is>
@@ -472,413 +512,484 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A2" s="2" t="n">
         <v>1990</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="11" t="n">
         <v>68232.00319999999</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="12" t="n">
         <v>10401.22</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="13" t="n">
         <v>1.57</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="12" t="n">
         <v>16329.91</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A3" s="2" t="n">
         <v>1991</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="11" t="n">
         <v>112024.0048</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="12" t="n">
         <v>17076.83</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="13" t="n">
         <v>1.547</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="12" t="n">
         <v>26417.85</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A4" s="2" t="n">
         <v>1992</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="11" t="n">
         <v>103828.9904</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="12" t="n">
         <v>15827.59</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="13" t="n">
         <v>1.496</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="12" t="n">
         <v>23678.08</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A5" s="2" t="n">
         <v>1993</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="11" t="n">
         <v>99461.9984</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="12" t="n">
         <v>15161.89</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="13" t="n">
         <v>1.496</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="12" t="n">
         <v>22682.19</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A6" s="2" t="n">
         <v>1994</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="11" t="n">
         <v>139800.0288</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="12" t="n">
         <v>21310.98</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="13" t="n">
         <v>1.47</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="12" t="n">
         <v>31327.13</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A7" s="2" t="n">
         <v>1995</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="11" t="n">
         <v>518657.0192</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="12" t="n">
         <v>79063.57000000001</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="13" t="n">
         <v>1.453</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="12" t="n">
         <v>114879.36</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A8" s="2" t="n">
         <v>1996</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="11" t="n">
         <v>146554.008</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="12" t="n">
         <v>22340.55</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="13" t="n">
         <v>1.418</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="12" t="n">
         <v>31678.9</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A9" s="2" t="n">
         <v>1997</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="11" t="n">
         <v>92033.97919999999</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="12" t="n">
         <v>14029.57</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="13" t="n">
         <v>1.403</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="12" t="n">
         <v>19683.49</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A10" s="2" t="n">
         <v>1999</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="11" t="n">
         <v>103974.032</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="12" t="n">
         <v>15849.7</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="13" t="n">
         <v>1.371</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="12" t="n">
         <v>21729.93</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A11" s="2" t="n">
         <v>2002</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="12" t="n">
         <v>33538</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="13" t="n">
         <v>1.307</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="12" t="n">
         <v>43834.17</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A12" s="2" t="n">
         <v>2003</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="12" t="n">
         <v>16007</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="13" t="n">
         <v>1.286</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="12" t="n">
         <v>20585</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A13" s="2" t="n">
         <v>2004</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="13" t="n">
         <v>1.266</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="12" t="n">
         <v>22788</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A14" s="2" t="n">
         <v>2005</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="13" t="n">
         <v>1.243</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="12" t="n">
         <v>22374</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A15" s="2" t="n">
         <v>2006</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="12" t="n">
         <v>22000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="13" t="n">
         <v>1.221</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="12" t="n">
         <v>26862</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A16" s="2" t="n">
         <v>2007</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="12" t="n">
         <v>17289</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="13" t="n">
         <v>1.201</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="12" t="n">
         <v>20764.09</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A17" s="2" t="n">
         <v>2008</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="12" t="n">
         <v>15084</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="13" t="n">
         <v>1.189</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="12" t="n">
         <v>17934.88</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A18" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="12" t="n">
         <v>18000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="13" t="n">
         <v>1.168</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="12" t="n">
         <v>21024</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A19" s="2" t="n">
         <v>2011</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="12" t="n">
         <v>21000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="13" t="n">
         <v>1.158</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="12" t="n">
         <v>24318</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A20" s="2" t="n">
         <v>2012</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="12" t="n">
         <v>27200</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="13" t="n">
         <v>1.135</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="12" t="n">
         <v>30872</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A21" s="2" t="n">
         <v>2013</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="12" t="n">
         <v>33600</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="13" t="n">
         <v>1.112</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="12" t="n">
         <v>37363.2</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A22" s="2" t="n">
         <v>2014</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="13" t="n">
         <v>1.098</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="12" t="n">
         <v>39528</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A23" s="2" t="n">
         <v>2015</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="13" t="n">
         <v>1.098</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="12" t="n">
         <v>39528</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A24" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="13" t="n">
         <v>1.097</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="12" t="n">
         <v>39492</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A25" s="2" t="n">
         <v>2017</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="12" t="n">
         <v>36000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="13" t="n">
         <v>1.097</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="12" t="n">
         <v>39492</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A26" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="12" t="n">
         <v>39000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="13" t="n">
         <v>1.089</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="12" t="n">
         <v>42471</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="27" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="5">
-        <f>SUM(C2:C26)</f>
+      <c r="C27" s="14">
+        <f>SUM(B2:B26)</f>
         <v/>
       </c>
-      <c r="E27" s="5">
-        <f>SUM(E2:E26)</f>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="14">
+        <f>SUM(D2:D26)</f>
         <v/>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Moyenne</t>
-        </is>
-      </c>
-      <c r="C28" s="5">
-        <f>AVERAGE(C2:C26)</f>
+      <c r="F27">
+        <f>SUM(F2:F26)</f>
         <v/>
       </c>
-      <c r="E28" s="5">
-        <f>AVERAGE(E2:E26)</f>
+    </row>
+    <row r="28" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Nombre années</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Revenu de base</t>
+        </is>
+      </c>
+      <c r="F30">
+        <f>F27/F29</f>
         <v/>
       </c>
     </row>
+    <row r="31" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31">
+        <f>F30*F31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>Nombre de trimestres</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Montant annuel</t>
+        </is>
+      </c>
+      <c r="F33">
+        <f>(F31*121)/167</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>Montont menseul</t>
+        </is>
+      </c>
+      <c r="F34">
+        <f>F33/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" thickTop="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Retraite_25Meilleures_Annees_2023.xlsx
+++ b/Retraite_25Meilleures_Annees_2023.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="6.1796875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,7 @@
           <t>Année</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Salaire brut (FRF)</t>
         </is>
@@ -902,10 +902,6 @@
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="14">
         <f>SUM(D2:D26)</f>
-        <v/>
-      </c>
-      <c r="F27">
-        <f>SUM(F2:F26)</f>
         <v/>
       </c>
     </row>
@@ -918,74 +914,74 @@
     <row r="29" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Nombre années</t>
         </is>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A30" s="2" t="n"/>
       <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Revenu de base</t>
         </is>
       </c>
-      <c r="F30">
-        <f>F27/F29</f>
+      <c r="E30" s="12">
+        <f>D27/D29</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="12" t="n">
+      <c r="D31" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="F31">
-        <f>F30*F31</f>
+      <c r="E31" s="12">
+        <f>D30*C31</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Nombre de trimestres</t>
         </is>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>121</v>
       </c>
     </row>
     <row r="33" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Montant annuel</t>
         </is>
       </c>
-      <c r="F33">
-        <f>(F31*121)/167</f>
+      <c r="E33" s="12">
+        <f>(D31*121)/167</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Montont menseul</t>
         </is>
       </c>
-      <c r="F34">
-        <f>F33/12</f>
+      <c r="E34" s="16">
+        <f>D33/12</f>
         <v/>
       </c>
     </row>

--- a/Retraite_25Meilleures_Annees_2023.xlsx
+++ b/Retraite_25Meilleures_Annees_2023.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="270" yWindow="550" windowWidth="18640" windowHeight="6740" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25 meilleures années" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,12 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ _€"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,25 +28,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,12 +44,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -72,48 +57,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -477,15 +436,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6.1796875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="15.54296875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="19.1796875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="19" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Année</t>
@@ -512,480 +472,462 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A2" s="2" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1990</v>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="2" t="n">
         <v>68232.00319999999</v>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="C2" s="2" t="n">
         <v>10401.22</v>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="2" t="n">
         <v>16329.91</v>
       </c>
     </row>
-    <row r="3" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A3" s="2" t="n">
+    <row r="3">
+      <c r="A3" t="n">
         <v>1991</v>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B3" s="2" t="n">
         <v>112024.0048</v>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="2" t="n">
         <v>17076.83</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="3" t="n">
         <v>1.547</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="2" t="n">
         <v>26417.85</v>
       </c>
     </row>
-    <row r="4" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A4" s="2" t="n">
+    <row r="4">
+      <c r="A4" t="n">
         <v>1992</v>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="2" t="n">
         <v>103828.9904</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="2" t="n">
         <v>15827.59</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="3" t="n">
         <v>1.496</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="2" t="n">
         <v>23678.08</v>
       </c>
     </row>
-    <row r="5" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A5" s="2" t="n">
+    <row r="5">
+      <c r="A5" t="n">
         <v>1993</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="2" t="n">
         <v>99461.9984</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="2" t="n">
         <v>15161.89</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="3" t="n">
         <v>1.496</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="2" t="n">
         <v>22682.19</v>
       </c>
     </row>
-    <row r="6" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A6" s="2" t="n">
+    <row r="6">
+      <c r="A6" t="n">
         <v>1994</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="2" t="n">
         <v>139800.0288</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="2" t="n">
         <v>21310.98</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="3" t="n">
         <v>1.47</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="2" t="n">
         <v>31327.13</v>
       </c>
     </row>
-    <row r="7" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A7" s="2" t="n">
+    <row r="7">
+      <c r="A7" t="n">
         <v>1995</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="2" t="n">
         <v>518657.0192</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="2" t="n">
         <v>79063.57000000001</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.453</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="2" t="n">
         <v>114879.36</v>
       </c>
     </row>
-    <row r="8" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A8" s="2" t="n">
+    <row r="8">
+      <c r="A8" t="n">
         <v>1996</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="2" t="n">
         <v>146554.008</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="2" t="n">
         <v>22340.55</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="3" t="n">
         <v>1.418</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="2" t="n">
         <v>31678.9</v>
       </c>
     </row>
-    <row r="9" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A9" s="2" t="n">
+    <row r="9">
+      <c r="A9" t="n">
         <v>1997</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="2" t="n">
         <v>92033.97919999999</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="2" t="n">
         <v>14029.57</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="3" t="n">
         <v>1.403</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="2" t="n">
         <v>19683.49</v>
       </c>
     </row>
-    <row r="10" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A10" s="2" t="n">
+    <row r="10">
+      <c r="A10" t="n">
         <v>1999</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="2" t="n">
         <v>103974.032</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="2" t="n">
         <v>15849.7</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="3" t="n">
         <v>1.371</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="2" t="n">
         <v>21729.93</v>
       </c>
     </row>
-    <row r="11" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A11" s="2" t="n">
+    <row r="11">
+      <c r="A11" t="n">
         <v>2002</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="2" t="n">
         <v>33538</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="3" t="n">
         <v>1.307</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="2" t="n">
         <v>43834.17</v>
       </c>
     </row>
-    <row r="12" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A12" s="2" t="n">
+    <row r="12">
+      <c r="A12" t="n">
         <v>2003</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="2" t="n">
         <v>16007</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="3" t="n">
         <v>1.286</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="2" t="n">
         <v>20585</v>
       </c>
     </row>
-    <row r="13" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A13" s="2" t="n">
+    <row r="13">
+      <c r="A13" t="n">
         <v>2004</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="3" t="n">
         <v>1.266</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="2" t="n">
         <v>22788</v>
       </c>
     </row>
-    <row r="14" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A14" s="2" t="n">
+    <row r="14">
+      <c r="A14" t="n">
         <v>2005</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="3" t="n">
         <v>1.243</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="2" t="n">
         <v>22374</v>
       </c>
     </row>
-    <row r="15" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A15" s="2" t="n">
+    <row r="15">
+      <c r="A15" t="n">
         <v>2006</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="2" t="n">
         <v>22000</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="3" t="n">
         <v>1.221</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="2" t="n">
         <v>26862</v>
       </c>
     </row>
-    <row r="16" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A16" s="2" t="n">
+    <row r="16">
+      <c r="A16" t="n">
         <v>2007</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="2" t="n">
         <v>17289</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="3" t="n">
         <v>1.201</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="2" t="n">
         <v>20764.09</v>
       </c>
     </row>
-    <row r="17" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A17" s="2" t="n">
+    <row r="17">
+      <c r="A17" t="n">
         <v>2008</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="2" t="n">
         <v>15084</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="3" t="n">
         <v>1.189</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="2" t="n">
         <v>17934.88</v>
       </c>
     </row>
-    <row r="18" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A18" s="2" t="n">
+    <row r="18">
+      <c r="A18" t="n">
         <v>2010</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="3" t="n">
         <v>1.168</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="2" t="n">
         <v>21024</v>
       </c>
     </row>
-    <row r="19" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A19" s="2" t="n">
+    <row r="19">
+      <c r="A19" t="n">
         <v>2011</v>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="2" t="n">
         <v>21000</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="3" t="n">
         <v>1.158</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="2" t="n">
         <v>24318</v>
       </c>
     </row>
-    <row r="20" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A20" s="2" t="n">
+    <row r="20">
+      <c r="A20" t="n">
         <v>2012</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="2" t="n">
         <v>27200</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="3" t="n">
         <v>1.135</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="2" t="n">
         <v>30872</v>
       </c>
     </row>
-    <row r="21" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A21" s="2" t="n">
+    <row r="21">
+      <c r="A21" t="n">
         <v>2013</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="2" t="n">
         <v>33600</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="3" t="n">
         <v>1.112</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="2" t="n">
         <v>37363.2</v>
       </c>
     </row>
-    <row r="22" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A22" s="2" t="n">
+    <row r="22">
+      <c r="A22" t="n">
         <v>2014</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="2" t="n">
         <v>36000</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="3" t="n">
         <v>1.098</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="2" t="n">
         <v>39528</v>
       </c>
     </row>
-    <row r="23" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A23" s="2" t="n">
+    <row r="23">
+      <c r="A23" t="n">
         <v>2015</v>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="2" t="n">
         <v>36000</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="3" t="n">
         <v>1.098</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="2" t="n">
         <v>39528</v>
       </c>
     </row>
-    <row r="24" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A24" s="2" t="n">
+    <row r="24">
+      <c r="A24" t="n">
         <v>2016</v>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="2" t="n">
         <v>36000</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="3" t="n">
         <v>1.097</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="2" t="n">
         <v>39492</v>
       </c>
     </row>
-    <row r="25" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A25" s="2" t="n">
+    <row r="25">
+      <c r="A25" t="n">
         <v>2017</v>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="2" t="n">
         <v>36000</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="3" t="n">
         <v>1.097</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="2" t="n">
         <v>39492</v>
       </c>
     </row>
-    <row r="26" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A26" s="2" t="n">
+    <row r="26">
+      <c r="A26" t="n">
         <v>2018</v>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="2" t="n">
         <v>39000</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="3" t="n">
         <v>1.089</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="2" t="n">
         <v>42471</v>
       </c>
     </row>
-    <row r="27" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="14">
-        <f>SUM(B2:B26)</f>
+      <c r="C27" s="5">
+        <f>SUM(C2:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="14">
-        <f>SUM(D2:D26)</f>
+      <c r="E27" s="5">
+        <f>SUM(E2:E26)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="15" t="n"/>
-    </row>
-    <row r="29" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="inlineStr">
+    <row r="29">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Nombre années</t>
         </is>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="E29" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="30" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="inlineStr">
+    <row r="30">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Revenu de base</t>
         </is>
       </c>
-      <c r="E30" s="12">
-        <f>D27/D29</f>
+      <c r="E30" s="2">
+        <f>E27/E29</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E31" s="12">
-        <f>D30*C31</f>
+    <row r="31">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E31" s="2">
+        <f>E30*0.5</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="inlineStr">
+    <row r="32">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Nombre de trimestres</t>
         </is>
       </c>
-      <c r="E32" s="15" t="n">
+      <c r="E32" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="33" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="inlineStr">
+    <row r="33">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Montant annuel</t>
         </is>
       </c>
-      <c r="E33" s="12">
-        <f>(D31*121)/167</f>
+      <c r="E33" s="2">
+        <f>(E31*121)/167</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="9" t="inlineStr">
+    <row r="34">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Montont menseul</t>
         </is>
       </c>
-      <c r="E34" s="16">
-        <f>D33/12</f>
+      <c r="E34" s="2">
+        <f>E33/12</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" thickTop="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Retraite_25Meilleures_Annees_2023.xlsx
+++ b/Retraite_25Meilleures_Annees_2023.xlsx
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +35,29 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,8 +70,14 @@
         <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,11 +85,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -70,6 +113,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,484 +500,527 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Année</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Salaire brut (FRF)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Salaire brut (EUR)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Coefficient 2023</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Montant au 1/1/2023</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="7" t="n">
         <v>1990</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="8" t="n">
         <v>68232.00319999999</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="9" t="n">
         <v>10401.22</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="10" t="n">
         <v>1.57</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="9" t="n">
         <v>16329.91</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="7" t="n">
         <v>1991</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="8" t="n">
         <v>112024.0048</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="9" t="n">
         <v>17076.83</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="10" t="n">
         <v>1.547</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="9" t="n">
         <v>26417.85</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="7" t="n">
         <v>1992</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="8" t="n">
         <v>103828.9904</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="9" t="n">
         <v>15827.59</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="10" t="n">
         <v>1.496</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="9" t="n">
         <v>23678.08</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="7" t="n">
         <v>1993</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="8" t="n">
         <v>99461.9984</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="9" t="n">
         <v>15161.89</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="10" t="n">
         <v>1.496</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="9" t="n">
         <v>22682.19</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="7" t="n">
         <v>1994</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="8" t="n">
         <v>139800.0288</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="9" t="n">
         <v>21310.98</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="10" t="n">
         <v>1.47</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="9" t="n">
         <v>31327.13</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="7" t="n">
         <v>1995</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="8" t="n">
         <v>518657.0192</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="9" t="n">
         <v>79063.57000000001</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="10" t="n">
         <v>1.453</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="9" t="n">
         <v>114879.36</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="7" t="n">
         <v>1996</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="8" t="n">
         <v>146554.008</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="9" t="n">
         <v>22340.55</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="10" t="n">
         <v>1.418</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="9" t="n">
         <v>31678.9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="7" t="n">
         <v>1997</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="8" t="n">
         <v>92033.97919999999</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="9" t="n">
         <v>14029.57</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="10" t="n">
         <v>1.403</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="9" t="n">
         <v>19683.49</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="7" t="n">
         <v>1999</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="8" t="n">
         <v>103974.032</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="9" t="n">
         <v>15849.7</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="10" t="n">
         <v>1.371</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="9" t="n">
         <v>21729.93</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="7" t="n">
         <v>2002</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="9" t="n">
         <v>33538</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="10" t="n">
         <v>1.307</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="9" t="n">
         <v>43834.17</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="7" t="n">
         <v>2003</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="9" t="n">
         <v>16007</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="10" t="n">
         <v>1.286</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="9" t="n">
         <v>20585</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="7" t="n">
         <v>2004</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="9" t="n">
         <v>18000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="10" t="n">
         <v>1.266</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="9" t="n">
         <v>22788</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="7" t="n">
         <v>2005</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="9" t="n">
         <v>18000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="10" t="n">
         <v>1.243</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="9" t="n">
         <v>22374</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="7" t="n">
         <v>2006</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="9" t="n">
         <v>22000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="10" t="n">
         <v>1.221</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="9" t="n">
         <v>26862</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="7" t="n">
         <v>2007</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="9" t="n">
         <v>17289</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="10" t="n">
         <v>1.201</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="9" t="n">
         <v>20764.09</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="9" t="n">
         <v>15084</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="10" t="n">
         <v>1.189</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="9" t="n">
         <v>17934.88</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="9" t="n">
         <v>18000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="10" t="n">
         <v>1.168</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="9" t="n">
         <v>21024</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="9" t="n">
         <v>21000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="10" t="n">
         <v>1.158</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="9" t="n">
         <v>24318</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="9" t="n">
         <v>27200</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="10" t="n">
         <v>1.135</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="9" t="n">
         <v>30872</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="9" t="n">
         <v>33600</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="10" t="n">
         <v>1.112</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="9" t="n">
         <v>37363.2</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="10" t="n">
         <v>1.098</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="9" t="n">
         <v>39528</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="10" t="n">
         <v>1.098</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="9" t="n">
         <v>39528</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="10" t="n">
         <v>1.097</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="9" t="n">
         <v>39492</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="10" t="n">
         <v>1.097</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="9" t="n">
         <v>39492</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="9" t="n">
         <v>39000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="10" t="n">
         <v>1.089</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="9" t="n">
         <v>42471</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C27" s="5">
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="12">
         <f>SUM(C2:C26)</f>
         <v/>
       </c>
-      <c r="E27" s="5">
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="12">
         <f>SUM(E2:E26)</f>
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+    </row>
     <row r="29">
-      <c r="D29" t="inlineStr">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Nombre années</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="7" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="30">
-      <c r="D30" t="inlineStr">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Revenu de base</t>
         </is>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="9">
         <f>E27/E29</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="D31" t="inlineStr">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="9">
         <f>E30*0.5</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="D32" t="inlineStr">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Nombre de trimestres</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="7" t="n">
         <v>121</v>
       </c>
     </row>
     <row r="33">
-      <c r="D33" t="inlineStr">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Montant annuel</t>
         </is>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="9">
         <f>(E31*121)/167</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Montont menseul</t>
-        </is>
-      </c>
-      <c r="E34" s="2">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Montant mensuel</t>
+        </is>
+      </c>
+      <c r="E34" s="14">
         <f>E33/12</f>
         <v/>
       </c>

--- a/Retraite_25Meilleures_Annees_2023.xlsx
+++ b/Retraite_25Meilleures_Annees_2023.xlsx
@@ -1,17 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="270" yWindow="550" windowWidth="18640" windowHeight="6740"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25 meilleures années" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="25 meilleures années" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>Année</t>
+  </si>
+  <si>
+    <t>Salaire brut (FRF)</t>
+  </si>
+  <si>
+    <t>Salaire brut (EUR)</t>
+  </si>
+  <si>
+    <t>Coefficient 2023</t>
+  </si>
+  <si>
+    <t>Montant au 1/1/2023</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Nombre années</t>
+  </si>
+  <si>
+    <t>Revenu de base</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>Nombre de trimestres</t>
+  </si>
+  <si>
+    <t>Montant annuel</t>
+  </si>
+  <si>
+    <t>Montant mensuel</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20,55 +60,42 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -104,99 +131,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -484,548 +437,522 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Année</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Salaire brut (FRF)</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Salaire brut (EUR)</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Coefficient 2023</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Montant au 1/1/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="n">
+    <row r="1" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A2" s="2">
         <v>1990</v>
       </c>
-      <c r="B2" s="8" t="n">
-        <v>68232.00319999999</v>
-      </c>
-      <c r="C2" s="9" t="n">
-        <v>10401.22</v>
-      </c>
-      <c r="D2" s="10" t="n">
+      <c r="B2" s="3">
+        <v>68232.003199999992</v>
+      </c>
+      <c r="C2" s="6">
+        <v>10401.219999999999</v>
+      </c>
+      <c r="D2" s="4">
         <v>1.57</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="6">
         <v>16329.91</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="n">
+    <row r="3" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A3" s="2">
         <v>1991</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="3">
         <v>112024.0048</v>
       </c>
-      <c r="C3" s="9" t="n">
-        <v>17076.83</v>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>1.547</v>
-      </c>
-      <c r="E3" s="9" t="n">
+      <c r="C3" s="6">
+        <v>17076.830000000002</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.5469999999999999</v>
+      </c>
+      <c r="E3" s="6">
         <v>26417.85</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="n">
+    <row r="4" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A4" s="2">
         <v>1992</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="3">
         <v>103828.9904</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="6">
         <v>15827.59</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="4">
         <v>1.496</v>
       </c>
-      <c r="E4" s="9" t="n">
-        <v>23678.08</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="E4" s="6">
+        <v>23678.080000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A5" s="2">
         <v>1993</v>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>99461.9984</v>
-      </c>
-      <c r="C5" s="9" t="n">
+      <c r="B5" s="3">
+        <v>99461.998399999997</v>
+      </c>
+      <c r="C5" s="6">
         <v>15161.89</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="4">
         <v>1.496</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="6">
         <v>22682.19</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
+    <row r="6" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A6" s="2">
         <v>1994</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="3">
         <v>139800.0288</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="6">
         <v>21310.98</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="4">
         <v>1.47</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="6">
         <v>31327.13</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="n">
+    <row r="7" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A7" s="2">
         <v>1995</v>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>518657.0192</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>79063.57000000001</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>1.453</v>
-      </c>
-      <c r="E7" s="9" t="n">
+      <c r="B7" s="3">
+        <v>518657.01919999998</v>
+      </c>
+      <c r="C7" s="6">
+        <v>79063.570000000007</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.4530000000000001</v>
+      </c>
+      <c r="E7" s="6">
         <v>114879.36</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
+    <row r="8" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A8" s="2">
         <v>1996</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="3">
         <v>146554.008</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="6">
         <v>22340.55</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>1.418</v>
-      </c>
-      <c r="E8" s="9" t="n">
+      <c r="D8" s="4">
+        <v>1.4179999999999999</v>
+      </c>
+      <c r="E8" s="6">
         <v>31678.9</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
+    <row r="9" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A9" s="2">
         <v>1997</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>92033.97919999999</v>
-      </c>
-      <c r="C9" s="9" t="n">
+      <c r="B9" s="3">
+        <v>92033.979199999987</v>
+      </c>
+      <c r="C9" s="6">
         <v>14029.57</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="4">
         <v>1.403</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>19683.49</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="E9" s="6">
+        <v>19683.490000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A10" s="2">
         <v>1999</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>103974.032</v>
-      </c>
-      <c r="C10" s="9" t="n">
+      <c r="B10" s="3">
+        <v>103974.03200000001</v>
+      </c>
+      <c r="C10" s="6">
         <v>15849.7</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="4">
         <v>1.371</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="6">
         <v>21729.93</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
+    <row r="11" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A11" s="2">
         <v>2002</v>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="9" t="n">
+      <c r="B11" s="2"/>
+      <c r="C11" s="6">
         <v>33538</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>1.307</v>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="4">
+        <v>1.3069999999999999</v>
+      </c>
+      <c r="E11" s="6">
         <v>43834.17</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
+    <row r="12" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A12" s="2">
         <v>2003</v>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="9" t="n">
+      <c r="B12" s="2"/>
+      <c r="C12" s="6">
         <v>16007</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="4">
         <v>1.286</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="6">
         <v>20585</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
+    <row r="13" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A13" s="2">
         <v>2004</v>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="9" t="n">
+      <c r="B13" s="2"/>
+      <c r="C13" s="6">
         <v>18000</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="4">
         <v>1.266</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="6">
         <v>22788</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
+    <row r="14" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A14" s="2">
         <v>2005</v>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="9" t="n">
+      <c r="B14" s="2"/>
+      <c r="C14" s="6">
         <v>18000</v>
       </c>
-      <c r="D14" s="10" t="n">
-        <v>1.243</v>
-      </c>
-      <c r="E14" s="9" t="n">
+      <c r="D14" s="4">
+        <v>1.2430000000000001</v>
+      </c>
+      <c r="E14" s="6">
         <v>22374</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
+    <row r="15" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A15" s="2">
         <v>2006</v>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="9" t="n">
+      <c r="B15" s="2"/>
+      <c r="C15" s="6">
         <v>22000</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>1.221</v>
-      </c>
-      <c r="E15" s="9" t="n">
+      <c r="D15" s="4">
+        <v>1.2210000000000001</v>
+      </c>
+      <c r="E15" s="6">
         <v>26862</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
+    <row r="16" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A16" s="2">
         <v>2007</v>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="9" t="n">
+      <c r="B16" s="2"/>
+      <c r="C16" s="6">
         <v>17289</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>1.201</v>
-      </c>
-      <c r="E16" s="9" t="n">
+      <c r="D16" s="4">
+        <v>1.2010000000000001</v>
+      </c>
+      <c r="E16" s="6">
         <v>20764.09</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
+    <row r="17" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A17" s="2">
         <v>2008</v>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="9" t="n">
+      <c r="B17" s="2"/>
+      <c r="C17" s="6">
         <v>15084</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>1.189</v>
-      </c>
-      <c r="E17" s="9" t="n">
+      <c r="D17" s="4">
+        <v>1.1890000000000001</v>
+      </c>
+      <c r="E17" s="6">
         <v>17934.88</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
+    <row r="18" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A18" s="2">
         <v>2010</v>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="9" t="n">
+      <c r="B18" s="2"/>
+      <c r="C18" s="6">
         <v>18000</v>
       </c>
-      <c r="D18" s="10" t="n">
-        <v>1.168</v>
-      </c>
-      <c r="E18" s="9" t="n">
+      <c r="D18" s="4">
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="E18" s="6">
         <v>21024</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
+    <row r="19" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A19" s="2">
         <v>2011</v>
       </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="9" t="n">
+      <c r="B19" s="2"/>
+      <c r="C19" s="6">
         <v>21000</v>
       </c>
-      <c r="D19" s="10" t="n">
-        <v>1.158</v>
-      </c>
-      <c r="E19" s="9" t="n">
+      <c r="D19" s="4">
+        <v>1.1579999999999999</v>
+      </c>
+      <c r="E19" s="6">
         <v>24318</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
+    <row r="20" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A20" s="2">
         <v>2012</v>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="9" t="n">
+      <c r="B20" s="2"/>
+      <c r="C20" s="6">
         <v>27200</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="4">
         <v>1.135</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="6">
         <v>30872</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
+    <row r="21" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A21" s="2">
         <v>2013</v>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="9" t="n">
+      <c r="B21" s="2"/>
+      <c r="C21" s="6">
         <v>33600</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>1.112</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>37363.2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="D21" s="4">
+        <v>1.1120000000000001</v>
+      </c>
+      <c r="E21" s="6">
+        <v>37363.199999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A22" s="2">
         <v>2014</v>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="9" t="n">
+      <c r="B22" s="2"/>
+      <c r="C22" s="6">
         <v>36000</v>
       </c>
-      <c r="D22" s="10" t="n">
-        <v>1.098</v>
-      </c>
-      <c r="E22" s="9" t="n">
+      <c r="D22" s="4">
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="E22" s="6">
         <v>39528</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
+    <row r="23" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A23" s="2">
         <v>2015</v>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="9" t="n">
+      <c r="B23" s="2"/>
+      <c r="C23" s="6">
         <v>36000</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>1.098</v>
-      </c>
-      <c r="E23" s="9" t="n">
+      <c r="D23" s="4">
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="E23" s="6">
         <v>39528</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
+    <row r="24" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A24" s="2">
         <v>2016</v>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="9" t="n">
+      <c r="B24" s="2"/>
+      <c r="C24" s="6">
         <v>36000</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="4">
         <v>1.097</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="6">
         <v>39492</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
+    <row r="25" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A25" s="2">
         <v>2017</v>
       </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="9" t="n">
+      <c r="B25" s="2"/>
+      <c r="C25" s="6">
         <v>36000</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="4">
         <v>1.097</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="6">
         <v>39492</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
+    <row r="26" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A26" s="2">
         <v>2018</v>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="9" t="n">
+      <c r="B26" s="2"/>
+      <c r="C26" s="6">
         <v>39000</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="4">
         <v>1.089</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="6">
         <v>42471</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="12">
+    <row r="27" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A27" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="7">
         <f>SUM(C2:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="12">
+        <v>633779.9</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="7">
         <f>SUM(E2:E26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Nombre années</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="n">
+        <v>797637.17999999993</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Revenu de base</t>
-        </is>
-      </c>
-      <c r="E30" s="9">
+    <row r="30" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="6">
         <f>E27/E29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="E31" s="9">
+        <v>31905.487199999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="6">
         <f>E30*0.5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Nombre de trimestres</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="n">
+        <v>15952.743599999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2">
         <v>121</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Montant annuel</t>
-        </is>
-      </c>
-      <c r="E33" s="9">
+    <row r="33" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="6">
         <f>(E31*121)/167</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n"/>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>Montant mensuel</t>
-        </is>
-      </c>
-      <c r="E34" s="14">
+        <v>11558.574704191615</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="9">
         <f>E33/12</f>
-        <v/>
-      </c>
-    </row>
+        <v>963.21455868263456</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" thickTop="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Retraite_25Meilleures_Annees_2023.xlsx
+++ b/Retraite_25Meilleures_Annees_2023.xlsx
@@ -1,57 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="550" windowWidth="18640" windowHeight="6740"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="270" yWindow="550" windowWidth="18640" windowHeight="6740" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="25 meilleures années" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25 meilleures années" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Année</t>
-  </si>
-  <si>
-    <t>Salaire brut (FRF)</t>
-  </si>
-  <si>
-    <t>Salaire brut (EUR)</t>
-  </si>
-  <si>
-    <t>Coefficient 2023</t>
-  </si>
-  <si>
-    <t>Montant au 1/1/2023</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Nombre années</t>
-  </si>
-  <si>
-    <t>Revenu de base</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>Nombre de trimestres</t>
-  </si>
-  <si>
-    <t>Montant annuel</t>
-  </si>
-  <si>
-    <t>Montant mensuel</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -62,37 +21,37 @@
   </numFmts>
   <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -132,24 +91,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -437,522 +463,550 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col width="6.1796875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="15.08984375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="15.54296875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="19.1796875" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A2" s="2">
+    <row r="1" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Année</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Salaire brut (FRF)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Salaire brut (EUR)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient 2023</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Montant au 1/1/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A2" s="2" t="n">
         <v>1990</v>
       </c>
-      <c r="B2" s="3">
-        <v>68232.003199999992</v>
-      </c>
-      <c r="C2" s="6">
-        <v>10401.219999999999</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="B2" s="3" t="n">
+        <v>33120</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>5049.11</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="6" t="n">
         <v>16329.91</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A3" s="2">
+    <row r="3" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A3" s="2" t="n">
         <v>1991</v>
       </c>
-      <c r="B3" s="3">
-        <v>112024.0048</v>
-      </c>
-      <c r="C3" s="6">
-        <v>17076.830000000002</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.5469999999999999</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="B3" s="3" t="n">
+        <v>112024</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>17077.95</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>26417.85</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A4" s="2">
+    <row r="4" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A4" s="2" t="n">
         <v>1992</v>
       </c>
-      <c r="B4" s="3">
-        <v>103828.9904</v>
-      </c>
-      <c r="C4" s="6">
-        <v>15827.59</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="B4" s="3" t="n">
+        <v>145507</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>22195.94</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>1.496</v>
       </c>
-      <c r="E4" s="6">
-        <v>23678.080000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A5" s="2">
+      <c r="E4" s="6" t="n">
+        <v>23678.08</v>
+      </c>
+    </row>
+    <row r="5" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A5" s="2" t="n">
         <v>1993</v>
       </c>
-      <c r="B5" s="3">
-        <v>99461.998399999997</v>
-      </c>
-      <c r="C5" s="6">
-        <v>15161.89</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="B5" s="3" t="n">
+        <v>178707</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>27256.95</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>1.496</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="6" t="n">
         <v>22682.19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A6" s="2">
+    <row r="6" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A6" s="2" t="n">
         <v>1994</v>
       </c>
-      <c r="B6" s="3">
-        <v>139800.0288</v>
-      </c>
-      <c r="C6" s="6">
-        <v>21310.98</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="B6" s="3" t="n">
+        <v>196188.24</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>29909.54</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>1.47</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="6" t="n">
         <v>31327.13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A7" s="2">
+    <row r="7" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A7" s="2" t="n">
         <v>1995</v>
       </c>
-      <c r="B7" s="3">
-        <v>518657.01919999998</v>
-      </c>
-      <c r="C7" s="6">
-        <v>79063.570000000007</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1.4530000000000001</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="B7" s="3" t="n">
+        <v>582944.08</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>88886.64</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>114879.36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A8" s="2">
+    <row r="8" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A8" s="2" t="n">
         <v>1996</v>
       </c>
-      <c r="B8" s="3">
-        <v>146554.008</v>
-      </c>
-      <c r="C8" s="6">
-        <v>22340.55</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1.4179999999999999</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="B8" s="3" t="n">
+        <v>115216.89</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>17573.22</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="E8" s="6" t="n">
         <v>31678.9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A9" s="2">
+    <row r="9" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A9" s="2" t="n">
         <v>1997</v>
       </c>
-      <c r="B9" s="3">
-        <v>92033.979199999987</v>
-      </c>
-      <c r="C9" s="6">
-        <v>14029.57</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="B9" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>6905.85</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>1.403</v>
       </c>
-      <c r="E9" s="6">
-        <v>19683.490000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A10" s="2">
+      <c r="E9" s="6" t="n">
+        <v>19683.49</v>
+      </c>
+    </row>
+    <row r="10" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A10" s="2" t="n">
         <v>1999</v>
       </c>
-      <c r="B10" s="3">
-        <v>103974.03200000001</v>
-      </c>
-      <c r="C10" s="6">
-        <v>15849.7</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="B10" s="3" t="n">
+        <v>51987</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>7927.23</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>1.371</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="6" t="n">
         <v>21729.93</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A11" s="2">
+    <row r="11" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A11" s="2" t="n">
         <v>2002</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="6">
-        <v>33538</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1.3069999999999999</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>9208</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>43834.17</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A12" s="2">
+    <row r="12" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A12" s="2" t="n">
         <v>2003</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="6">
-        <v>16007</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="6" t="n">
+        <v>9031</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>1.286</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="6" t="n">
         <v>20585</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A13" s="2">
+    <row r="13" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A13" s="2" t="n">
         <v>2004</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="6">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="4" t="n">
         <v>1.266</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="6" t="n">
         <v>22788</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A14" s="2">
+    <row r="14" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A14" s="2" t="n">
         <v>2005</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="6">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="D14" s="4">
-        <v>1.2430000000000001</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="D14" s="4" t="n">
+        <v>1.243</v>
+      </c>
+      <c r="E14" s="6" t="n">
         <v>22374</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A15" s="2">
+    <row r="15" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A15" s="2" t="n">
         <v>2006</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="6">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="6" t="n">
         <v>22000</v>
       </c>
-      <c r="D15" s="4">
-        <v>1.2210000000000001</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="D15" s="4" t="n">
+        <v>1.221</v>
+      </c>
+      <c r="E15" s="6" t="n">
         <v>26862</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A16" s="2">
+    <row r="16" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A16" s="2" t="n">
         <v>2007</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="6">
-        <v>17289</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1.2010000000000001</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="6" t="n">
+        <v>17288.52</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="E16" s="6" t="n">
         <v>20764.09</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A17" s="2">
+    <row r="17" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A17" s="2" t="n">
         <v>2008</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="6">
-        <v>15084</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1.1890000000000001</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="6" t="n">
+        <v>15057.53</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="E17" s="6" t="n">
         <v>17934.88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A18" s="2">
+    <row r="18" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A18" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="6">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="D18" s="4">
-        <v>1.1679999999999999</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="D18" s="4" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="E18" s="6" t="n">
         <v>21024</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A19" s="2">
+    <row r="19" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A19" s="2" t="n">
         <v>2011</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="6">
-        <v>21000</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1.1579999999999999</v>
-      </c>
-      <c r="E19" s="6">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="6" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="E19" s="6" t="n">
         <v>24318</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A20" s="2">
+    <row r="20" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A20" s="2" t="n">
         <v>2012</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="6">
-        <v>27200</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="6" t="n">
+        <v>27117.04</v>
+      </c>
+      <c r="D20" s="4" t="n">
         <v>1.135</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="6" t="n">
         <v>30872</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A21" s="2">
+    <row r="21" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A21" s="2" t="n">
         <v>2013</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="6">
-        <v>33600</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1.1120000000000001</v>
-      </c>
-      <c r="E21" s="6">
-        <v>37363.199999999997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A22" s="2">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>33185.2</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>37363.2</v>
+      </c>
+    </row>
+    <row r="22" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A22" s="2" t="n">
         <v>2014</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="6">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="6" t="n">
         <v>36000</v>
       </c>
-      <c r="D22" s="4">
-        <v>1.0980000000000001</v>
-      </c>
-      <c r="E22" s="6">
+      <c r="D22" s="4" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="E22" s="6" t="n">
         <v>39528</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A23" s="2">
+    <row r="23" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A23" s="2" t="n">
         <v>2015</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="6">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="6" t="n">
         <v>36000</v>
       </c>
-      <c r="D23" s="4">
-        <v>1.0980000000000001</v>
-      </c>
-      <c r="E23" s="6">
+      <c r="D23" s="4" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="E23" s="6" t="n">
         <v>39528</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A24" s="2">
+    <row r="24" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A24" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="6">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="6" t="n">
         <v>36000</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="4" t="n">
         <v>1.097</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="6" t="n">
         <v>39492</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A25" s="2">
+    <row r="25" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A25" s="2" t="n">
         <v>2017</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="6">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="6" t="n">
         <v>36000</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="4" t="n">
         <v>1.097</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="6" t="n">
         <v>39492</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A26" s="2">
+    <row r="26" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A26" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="6">
-        <v>39000</v>
-      </c>
-      <c r="D26" s="4">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="6" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D26" s="4" t="n">
         <v>1.089</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="6" t="n">
         <v>42471</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A27" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="2"/>
+    <row r="27" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
       <c r="C27" s="7">
         <f>SUM(C2:C26)</f>
-        <v>633779.9</v>
-      </c>
-      <c r="D27" s="2"/>
+        <v/>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="7">
         <f>SUM(E2:E26)</f>
-        <v>797637.17999999993</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Nombre années</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2" t="s">
-        <v>7</v>
+    <row r="30" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Revenu de base</t>
+        </is>
       </c>
       <c r="E30" s="6">
         <f>E27/E29</f>
-        <v>31905.487199999996</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
       </c>
       <c r="E31" s="6">
         <f>E30*0.5</f>
-        <v>15952.743599999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Nombre de trimestres</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2" t="s">
-        <v>10</v>
+    <row r="33" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Montant annuel</t>
+        </is>
       </c>
       <c r="E33" s="6">
         <f>(E31*121)/167</f>
-        <v>11558.574704191615</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15.5" thickTop="1" thickBot="1">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="8" t="s">
-        <v>11</v>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15.5" customHeight="1" thickBot="1" thickTop="1">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Montant mensuel</t>
+        </is>
       </c>
       <c r="E34" s="9">
         <f>E33/12</f>
-        <v>963.21455868263456</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" thickTop="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" thickTop="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>